--- a/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
+++ b/data/daschland_ontology/daschland (Alice in DaSCHland)/resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/daschland_ontology/daschland (Alice in DaSCHland)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noraammann/Documents/Cloned_GitHub/daschland-scripts/data/daschland_ontology/daschland (Alice in DaSCHland)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C90DF7-5718-9B40-9313-9E6F983C8350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675C9A28-9C0D-CA47-B1A4-F0D1DFAF5CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31360" yWindow="800" windowWidth="34560" windowHeight="21580" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20500" tabRatio="500" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">Audio!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">BookCover!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">BookEdition!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Character!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">BookEdition!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Character!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">classes!$A$1:$M$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Event!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Image!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Location!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Story!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Location!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Story!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">StoryChapter!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">Video!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">Video!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -1036,7 +1036,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="225">
   <si>
     <t>name</t>
   </si>
@@ -1708,13 +1708,16 @@
   </si>
   <si>
     <t>isPartOfStoryChapter</t>
+  </si>
+  <si>
+    <t>hasWikidataLink</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1786,6 +1789,11 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3885,78 +3893,78 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="9">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="10">
+        <v>65</v>
+      </c>
+      <c r="C6">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="A8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>7</v>
       </c>
     </row>
@@ -6928,7 +6936,7 @@
       <c r="B997" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C5" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
@@ -6940,10 +6948,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -6965,7 +6973,18 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7035,7 +7054,7 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7045,8 +7064,8 @@
       <c r="B3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="10">
-        <v>3</v>
+      <c r="C3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7057,7 +7076,7 @@
         <v>65</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7068,7 +7087,7 @@
         <v>65</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7079,7 +7098,7 @@
         <v>65</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -7090,7 +7109,7 @@
         <v>67</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7101,7 +7120,7 @@
         <v>65</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7112,7 +7131,7 @@
         <v>65</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7123,7 +7142,7 @@
         <v>65</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7134,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8352,7 +8371,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:C996"/>
+  <dimension ref="A1:C997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
@@ -8385,7 +8404,7 @@
       <c r="A3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C3">
@@ -8394,10 +8413,10 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="9">
-        <v>1</v>
+        <v>224</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -8405,20 +8424,20 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>65</v>
+        <v>142</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C6">
@@ -8426,11 +8445,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>138</v>
+      <c r="A7" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -8438,10 +8457,10 @@
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -8449,7 +8468,7 @@
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>65</v>
@@ -8459,17 +8478,27 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1</v>
+      <c r="A10" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9455,12 +9484,14 @@
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000010000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C10">
-      <sortCondition ref="C1:C10"/>
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0000-000010000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C11">
+      <sortCondition ref="C1:C11"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
   </hyperlinks>
@@ -9472,7 +9503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C998"/>
+  <dimension ref="A1:C999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -9547,12 +9578,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>215</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>224</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -9560,7 +9591,7 @@
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>67</v>
@@ -9571,7 +9602,7 @@
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>67</v>
@@ -9582,7 +9613,7 @@
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>67</v>
@@ -9592,8 +9623,8 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
-        <v>138</v>
+      <c r="A11" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>67</v>
@@ -9604,10 +9635,10 @@
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -9615,7 +9646,7 @@
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>65</v>
@@ -9625,18 +9656,26 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B15" s="9">
         <v>1</v>
       </c>
-      <c r="C14" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="9"/>
+      <c r="C15">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="9"/>
@@ -12587,12 +12626,16 @@
     <row r="998" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B998" s="9"/>
     </row>
+    <row r="999" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B999" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C14">
-      <sortCondition ref="C1:C14"/>
+  <autoFilter ref="A1:C12" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C15">
+      <sortCondition ref="C1:C15"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -12623,160 +12666,164 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="9">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="6">
         <v>1</v>
-      </c>
-      <c r="C2" s="6">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C7" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="C12" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C14" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>65</v>
+      <c r="A15" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="9">
+        <v>1</v>
       </c>
       <c r="C15" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:C12" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C15">
+      <sortCondition ref="C1:C15"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
@@ -12828,57 +12875,57 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="9">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="C4" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>65</v>
+      <c r="A5" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="C5" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C7" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>65</v>
+      <c r="A8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1</v>
       </c>
       <c r="C8" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12898,7 +12945,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C993"/>
+  <dimension ref="A1:C994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
@@ -12936,7 +12983,7 @@
       <c r="B3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>2</v>
       </c>
     </row>
@@ -12947,13 +12994,13 @@
       <c r="B4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>140</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>224</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>65</v>
@@ -12963,8 +13010,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>139</v>
+      <c r="A6" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>65</v>
@@ -12974,11 +13021,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>67</v>
+      <c r="A7" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -12986,10 +13033,10 @@
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -12997,7 +13044,7 @@
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>65</v>
@@ -13007,18 +13054,26 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1</v>
+      <c r="A10" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="9"/>
+      <c r="A11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="9"/>
@@ -15966,12 +16021,16 @@
     <row r="993" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B993" s="9"/>
     </row>
+    <row r="994" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B994" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C10">
-      <sortCondition ref="C1:C10"/>
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C11">
+      <sortCondition ref="C1:C11"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
@@ -15983,7 +16042,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C998"/>
+  <dimension ref="A1:C999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -16003,29 +16062,29 @@
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="9">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="6">
         <v>1</v>
-      </c>
-      <c r="C2" s="6">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>67</v>
@@ -16036,10 +16095,10 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -16047,10 +16106,10 @@
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="6">
         <v>5</v>
@@ -16058,7 +16117,7 @@
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>67</v>
@@ -16067,12 +16126,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>79</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>224</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" s="6">
         <v>7</v>
@@ -16112,7 +16171,15 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="9"/>
+      <c r="A12" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="9"/>
@@ -19057,13 +19124,16 @@
     <row r="993" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B993" s="9"/>
     </row>
-    <row r="994" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B994" s="9"/>
+    </row>
     <row r="995" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="996" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="997" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="998" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:C8" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" location="resource-cardinalities" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
@@ -19094,101 +19164,101 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="9">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="6">
         <v>1</v>
-      </c>
-      <c r="C2" s="6">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="6">
-        <v>5</v>
+      <c r="C7" s="10">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="10">
-        <v>10</v>
+      <c r="A10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="9">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
